--- a/Result/profitability/1732.xlsx
+++ b/Result/profitability/1732.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>0.17375</v>
+        <v>0.19625</v>
       </c>
       <c r="N2" t="n">
-        <v>41.44875</v>
+        <v>41.305</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.17875</v>
+        <v>0.2125</v>
       </c>
       <c r="N3" t="n">
-        <v>41.21375</v>
+        <v>41.44625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17125</v>
+        <v>0.185</v>
       </c>
       <c r="N4" t="n">
-        <v>41.8275</v>
+        <v>42.1475</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>0.13</v>
+        <v>0.17125</v>
       </c>
       <c r="N5" t="n">
-        <v>42.43625</v>
+        <v>42.38874999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.17875</v>
+        <v>0.17375</v>
       </c>
       <c r="N6" t="n">
-        <v>42.97125</v>
+        <v>42.95875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.16875</v>
+        <v>0.16125</v>
       </c>
       <c r="N7" t="n">
-        <v>43.605</v>
+        <v>43.56875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.15375</v>
+        <v>0.1425</v>
       </c>
       <c r="N8" t="n">
-        <v>44.34625</v>
+        <v>44.32375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.11125</v>
       </c>
       <c r="N10" t="n">
-        <v>45.28749999999999</v>
+        <v>45.2875</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>193</v>
+      </c>
+      <c r="D75" t="n">
+        <v>113</v>
+      </c>
+      <c r="E75" t="n">
+        <v>81</v>
+      </c>
+      <c r="F75" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>17</v>
+      </c>
+      <c r="K75" t="n">
+        <v>11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>41.36</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08999999999999997</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.004303131723643272</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.714285714285714</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3800000000000026</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.00904116107542241</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
